--- a/output/pdf_financials_xlsx/GDP.xlsx
+++ b/output/pdf_financials_xlsx/GDP.xlsx
@@ -5909,40 +5909,40 @@
         <v>4.579675</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>4.741085</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>4.764655</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>4.812111</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>4.924267</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>4.99567</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>5.32755</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>5.3231</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>5.878603</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>5.842878</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>6.081689</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>6.266727</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>6.489449</v>
       </c>
     </row>
     <row r="93">
@@ -9851,7 +9851,11 @@
           <t>Reserves (Note 7,8,9)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -10839,7 +10843,11 @@
           <t>Reserves (Notes 6 and 8)</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -11399,7 +11407,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -11700,7 +11712,11 @@
           <t>Reserves (Notes 7 and 8)</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -12399,7 +12415,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -12999,7 +13019,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -13502,7 +13526,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GDP.xlsx
+++ b/output/pdf_financials_xlsx/GDP.xlsx
@@ -940,22 +940,22 @@
         <v>0.151877</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.19274</v>
+        <v>0.322699</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.27616</v>
+        <v>0.823578</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.259212</v>
+        <v>0.634449</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.307132</v>
+        <v>0.6856370000000001</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.233291</v>
+        <v>1.153845</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.303522</v>
+        <v>0.789037</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>0.722596</v>
@@ -998,22 +998,22 @@
         <v>-0.151877</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.19274</v>
+        <v>-0.322699</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.27616</v>
+        <v>-0.823578</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.259212</v>
+        <v>-0.634449</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.307132</v>
+        <v>-0.6856370000000001</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-0.233291</v>
+        <v>-1.153845</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.303522</v>
+        <v>-0.789037</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>-0.722596</v>
@@ -2398,55 +2398,55 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.369237</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.253909</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.8907119999999999</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.926465</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.168852</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.007964000000000001</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.0009840000000000001</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.027401</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.03961</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.023716</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.005117</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.006883</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.053979</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.010965</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.049978</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.465251</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.276875</v>
       </c>
     </row>
     <row r="35">
@@ -2514,55 +2514,55 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.369237</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.253909</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.8907119999999999</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.926465</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.168852</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.007964000000000001</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.0009840000000000001</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.027401</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.03961</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.023716</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.005117</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.006883</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.053979</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.010965</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.049978</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.465251</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.276875</v>
       </c>
     </row>
     <row r="37">
@@ -3210,55 +3210,55 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.375732</v>
+        <v>0.006495</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.259158</v>
+        <v>0.005249</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.920632</v>
+        <v>0.02992</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.972516</v>
+        <v>0.046051</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.266492</v>
+        <v>0.09764</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.030482</v>
+        <v>0.022518</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.027401</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.03961</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.023716</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.118016</v>
+        <v>0.112899</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.006883</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.23882</v>
+        <v>0.184841</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.014565</v>
+        <v>0.0036</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.058847</v>
+        <v>0.008869</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.471291</v>
+        <v>0.00604</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.276875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">
@@ -30023,7 +30023,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -34583,7 +34583,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -35397,7 +35397,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
